--- a/Histórico/Acumulado Ávila.xlsx
+++ b/Histórico/Acumulado Ávila.xlsx
@@ -1,81 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python proyectos\Meteo Dash\Meteo\Histórico\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB5385F-C4A5-4D8E-A83C-586D3E71BC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Fecha y hora oficial</t>
-  </si>
-  <si>
-    <t>Temperatura (ºC)</t>
-  </si>
-  <si>
-    <t>Velocidad del viento (km/h)</t>
-  </si>
-  <si>
-    <t>Dirección del viento</t>
-  </si>
-  <si>
-    <t>Racha (km/h)</t>
-  </si>
-  <si>
-    <t>Dirección de racha</t>
-  </si>
-  <si>
-    <t>Precipitación (mm)</t>
-  </si>
-  <si>
-    <t>Presión (hPa)</t>
-  </si>
-  <si>
-    <t>Tendencia (hPa)</t>
-  </si>
-  <si>
-    <t>Humedad (%)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -90,46 +49,96 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -417,169 +426,1277 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha y hora oficial</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Temperatura (ºC)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Velocidad del viento (km/h)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dirección del viento</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Racha (km/h)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dirección de racha</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Precipitación (mm)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Presión (hPa)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tendencia (hPa)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Humedad (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46228.83333333334</v>
+      </c>
+      <c r="B2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>890.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46228.79166666666</v>
+      </c>
+      <c r="B3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>890.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46228.75</v>
+      </c>
+      <c r="B4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>890</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46228.70833333334</v>
+      </c>
+      <c r="B5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>889.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46228.66666666666</v>
+      </c>
+      <c r="B6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>36</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>889.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46228.625</v>
+      </c>
+      <c r="B7" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>38</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46228.58333333334</v>
+      </c>
+      <c r="B8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>889.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46228.54166666666</v>
+      </c>
+      <c r="B9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>29</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>890</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46228.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>889.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46228.45833333334</v>
+      </c>
+      <c r="B11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>32</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46228.41666666666</v>
+      </c>
+      <c r="B12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>889.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46228.375</v>
+      </c>
+      <c r="B13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>889.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46228.33333333334</v>
+      </c>
+      <c r="B14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>889.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46228.29166666666</v>
+      </c>
+      <c r="B15" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>889</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46228.25</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>889.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46228.20833333334</v>
+      </c>
+      <c r="B17" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>889.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46228.16666666666</v>
+      </c>
+      <c r="B18" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>889.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46228.125</v>
+      </c>
+      <c r="B19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>889.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46228.08333333334</v>
+      </c>
+      <c r="B20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>889.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46228.04166666666</v>
+      </c>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>890.1</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>45148.833333333343</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>45148.791666666657</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="J21" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B22" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>889.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46227.95833333334</v>
+      </c>
+      <c r="B23" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>889.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46227.91666666666</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>30</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>889.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46227.875</v>
+      </c>
+      <c r="B25" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>34</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>888.8</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45148.83333333334</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45148.79166666666</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
         <v>45148.75</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>45148.708333333343</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>45148.666666666657</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45148.70833333334</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45148.66666666666</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
         <v>45148.625</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>45148.583333333343</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>45148.541666666657</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45148.58333333334</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45148.54166666666</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
         <v>45148.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>45148.458333333343</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>45148.416666666657</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45148.45833333334</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45148.41666666666</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
         <v>45148.375</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>45148.333333333343</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>45148.291666666657</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45148.33333333334</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45148.29166666666</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
         <v>45148.25</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>45148.208333333343</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>45148.166666666657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45148.20833333334</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45148.16666666666</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
         <v>45148.125</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>45148.083333333343</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>45148.041666666657</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45148.08333333334</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45148.04166666666</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
         <v>45148</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>45147.958333333343</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>45147.916666666657</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45147.95833333334</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45147.91666666666</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
         <v>45147.875</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>45147.833333333343</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45147.83333333334</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
